--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127123849</v>
+        <v>127125627</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>80143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595811</v>
+        <v>595873</v>
       </c>
       <c r="R5" t="n">
-        <v>6986388</v>
+        <v>6986327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127125627</v>
+        <v>127123849</v>
       </c>
       <c r="B6" t="n">
-        <v>80112</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595873</v>
+        <v>595811</v>
       </c>
       <c r="R6" t="n">
-        <v>6986327</v>
+        <v>6986388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
         <v>127124770</v>
       </c>
       <c r="B8" t="n">
-        <v>98281</v>
+        <v>98356</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127124162</v>
       </c>
       <c r="B9" t="n">
-        <v>91210</v>
+        <v>91284</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127123771</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127124585</v>
+        <v>127125706</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>80080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595752</v>
+        <v>595873</v>
       </c>
       <c r="R11" t="n">
-        <v>6986290</v>
+        <v>6986327</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127125706</v>
+        <v>127124585</v>
       </c>
       <c r="B12" t="n">
-        <v>80049</v>
+        <v>80114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595873</v>
+        <v>595752</v>
       </c>
       <c r="R12" t="n">
-        <v>6986327</v>
+        <v>6986290</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
         <v>127124329</v>
       </c>
       <c r="B13" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127123933</v>
+        <v>127125760</v>
       </c>
       <c r="B14" t="n">
-        <v>80112</v>
+        <v>80074</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595828</v>
+        <v>595888</v>
       </c>
       <c r="R14" t="n">
-        <v>6986375</v>
+        <v>6986327</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127125760</v>
+        <v>127123933</v>
       </c>
       <c r="B15" t="n">
-        <v>80043</v>
+        <v>80143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595888</v>
+        <v>595828</v>
       </c>
       <c r="R15" t="n">
-        <v>6986327</v>
+        <v>6986375</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
         <v>127125279</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124387</v>
+        <v>127124805</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595748</v>
+        <v>595706</v>
       </c>
       <c r="R18" t="n">
-        <v>6986317</v>
+        <v>6986223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2348,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,45 +2374,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124623</v>
+        <v>127124387</v>
       </c>
       <c r="B19" t="n">
-        <v>97242</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595755</v>
+        <v>595748</v>
       </c>
       <c r="R19" t="n">
-        <v>6986253</v>
+        <v>6986317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2450,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124805</v>
+        <v>127123757</v>
       </c>
       <c r="B20" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,16 +2492,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2516,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595706</v>
+        <v>595824</v>
       </c>
       <c r="R20" t="n">
-        <v>6986223</v>
+        <v>6986427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2557,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127123757</v>
+        <v>127124623</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>97317</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595824</v>
+        <v>595755</v>
       </c>
       <c r="R21" t="n">
-        <v>6986427</v>
+        <v>6986253</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127125627</v>
+        <v>127123849</v>
       </c>
       <c r="B5" t="n">
-        <v>80143</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595873</v>
+        <v>595811</v>
       </c>
       <c r="R5" t="n">
-        <v>6986327</v>
+        <v>6986388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127123849</v>
+        <v>127125627</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>80146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595811</v>
+        <v>595873</v>
       </c>
       <c r="R6" t="n">
-        <v>6986388</v>
+        <v>6986327</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1295,7 +1295,7 @@
         <v>127124770</v>
       </c>
       <c r="B8" t="n">
-        <v>98356</v>
+        <v>98362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127124162</v>
       </c>
       <c r="B9" t="n">
-        <v>91284</v>
+        <v>91290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127123771</v>
       </c>
       <c r="B10" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127125706</v>
+        <v>127124585</v>
       </c>
       <c r="B11" t="n">
-        <v>80080</v>
+        <v>80117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595873</v>
+        <v>595752</v>
       </c>
       <c r="R11" t="n">
-        <v>6986327</v>
+        <v>6986290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127124585</v>
+        <v>127125706</v>
       </c>
       <c r="B12" t="n">
-        <v>80114</v>
+        <v>80083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595752</v>
+        <v>595873</v>
       </c>
       <c r="R12" t="n">
-        <v>6986290</v>
+        <v>6986327</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,7 +1780,7 @@
         <v>127124329</v>
       </c>
       <c r="B13" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127125760</v>
+        <v>127123933</v>
       </c>
       <c r="B14" t="n">
-        <v>80074</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595888</v>
+        <v>595828</v>
       </c>
       <c r="R14" t="n">
-        <v>6986327</v>
+        <v>6986375</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127123933</v>
+        <v>127125760</v>
       </c>
       <c r="B15" t="n">
-        <v>80143</v>
+        <v>80077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595828</v>
+        <v>595888</v>
       </c>
       <c r="R15" t="n">
-        <v>6986375</v>
+        <v>6986327</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127125279</v>
+        <v>127125418</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,34 +2079,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595812</v>
+        <v>595850</v>
       </c>
       <c r="R16" t="n">
-        <v>6986327</v>
+        <v>6986354</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,6 +2144,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2165,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125418</v>
+        <v>127125279</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2176,39 +2186,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595850</v>
+        <v>595812</v>
       </c>
       <c r="R17" t="n">
-        <v>6986354</v>
+        <v>6986327</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2241,11 +2246,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2591,7 +2591,7 @@
         <v>127124623</v>
       </c>
       <c r="B21" t="n">
-        <v>97317</v>
+        <v>97323</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127123849</v>
+        <v>127125627</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595811</v>
+        <v>595873</v>
       </c>
       <c r="R5" t="n">
-        <v>6986388</v>
+        <v>6986327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127125627</v>
+        <v>127123849</v>
       </c>
       <c r="B6" t="n">
-        <v>80146</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595873</v>
+        <v>595811</v>
       </c>
       <c r="R6" t="n">
-        <v>6986327</v>
+        <v>6986388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,38 +1185,33 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127123720</v>
+        <v>127124770</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>98362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595830</v>
+        <v>595711</v>
       </c>
       <c r="R7" t="n">
-        <v>6986436</v>
+        <v>6986237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,33 +1282,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127124770</v>
+        <v>127123720</v>
       </c>
       <c r="B8" t="n">
-        <v>98362</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1327,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595711</v>
+        <v>595830</v>
       </c>
       <c r="R8" t="n">
-        <v>6986237</v>
+        <v>6986436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1358,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2068,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127125418</v>
+        <v>127125279</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,39 +2079,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595850</v>
+        <v>595812</v>
       </c>
       <c r="R16" t="n">
-        <v>6986354</v>
+        <v>6986327</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,11 +2139,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2175,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125279</v>
+        <v>127125418</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,34 +2176,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595812</v>
+        <v>595850</v>
       </c>
       <c r="R17" t="n">
-        <v>6986327</v>
+        <v>6986354</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2246,6 +2241,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124805</v>
+        <v>127124387</v>
       </c>
       <c r="B18" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595706</v>
+        <v>595748</v>
       </c>
       <c r="R18" t="n">
-        <v>6986223</v>
+        <v>6986317</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2374,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124387</v>
+        <v>127123757</v>
       </c>
       <c r="B19" t="n">
         <v>57657</v>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595748</v>
+        <v>595824</v>
       </c>
       <c r="R19" t="n">
-        <v>6986317</v>
+        <v>6986427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,50 +2486,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127123757</v>
+        <v>127124623</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>97323</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221946</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595824</v>
+        <v>595755</v>
       </c>
       <c r="R20" t="n">
-        <v>6986427</v>
+        <v>6986253</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,11 +2557,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,45 +2583,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124623</v>
+        <v>127124805</v>
       </c>
       <c r="B21" t="n">
-        <v>97323</v>
+        <v>57654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595755</v>
+        <v>595706</v>
       </c>
       <c r="R21" t="n">
-        <v>6986253</v>
+        <v>6986223</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127123865</v>
+        <v>127123617</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>57657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,27 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595811</v>
+        <v>595826</v>
       </c>
       <c r="R3" t="n">
-        <v>6986388</v>
+        <v>6986441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127123617</v>
+        <v>127123865</v>
       </c>
       <c r="B4" t="n">
-        <v>57657</v>
+        <v>57817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,27 +900,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595826</v>
+        <v>595811</v>
       </c>
       <c r="R4" t="n">
-        <v>6986441</v>
+        <v>6986388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1188,7 +1188,7 @@
         <v>127124770</v>
       </c>
       <c r="B7" t="n">
-        <v>98362</v>
+        <v>98363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127124162</v>
       </c>
       <c r="B9" t="n">
-        <v>91290</v>
+        <v>91291</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127124329</v>
+        <v>127123933</v>
       </c>
       <c r="B13" t="n">
-        <v>91325</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595748</v>
+        <v>595828</v>
       </c>
       <c r="R13" t="n">
-        <v>6986317</v>
+        <v>6986375</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,32 +1874,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127123933</v>
+        <v>127124329</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595828</v>
+        <v>595748</v>
       </c>
       <c r="R14" t="n">
-        <v>6986375</v>
+        <v>6986317</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124387</v>
+        <v>127124805</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595748</v>
+        <v>595706</v>
       </c>
       <c r="R18" t="n">
-        <v>6986317</v>
+        <v>6986223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2348,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2374,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127123757</v>
+        <v>127124387</v>
       </c>
       <c r="B19" t="n">
         <v>57657</v>
@@ -2419,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595824</v>
+        <v>595748</v>
       </c>
       <c r="R19" t="n">
-        <v>6986427</v>
+        <v>6986317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,45 +2481,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124623</v>
+        <v>127123757</v>
       </c>
       <c r="B20" t="n">
-        <v>97323</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595755</v>
+        <v>595824</v>
       </c>
       <c r="R20" t="n">
-        <v>6986253</v>
+        <v>6986427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,6 +2557,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124805</v>
+        <v>127124623</v>
       </c>
       <c r="B21" t="n">
-        <v>57654</v>
+        <v>97324</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595706</v>
+        <v>595755</v>
       </c>
       <c r="R21" t="n">
-        <v>6986223</v>
+        <v>6986253</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1185,33 +1185,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127124770</v>
+        <v>127123720</v>
       </c>
       <c r="B7" t="n">
-        <v>98363</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1220,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595711</v>
+        <v>595830</v>
       </c>
       <c r="R7" t="n">
-        <v>6986237</v>
+        <v>6986436</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,38 +1292,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127123720</v>
+        <v>127124770</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>98363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1322,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595830</v>
+        <v>595711</v>
       </c>
       <c r="R8" t="n">
-        <v>6986436</v>
+        <v>6986237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2790,6 +2790,495 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127427818</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98443</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>595803</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6986267</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127427830</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80117</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>595803</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6986267</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127427437</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>595800</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6986411</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127428796</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>595865</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6986347</v>
+      </c>
+      <c r="S26" t="n">
+        <v>15</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127427844</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högåsen, Högåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>595802</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6986266</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -1185,38 +1185,33 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127123720</v>
+        <v>127124770</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>98363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595830</v>
+        <v>595711</v>
       </c>
       <c r="R7" t="n">
-        <v>6986436</v>
+        <v>6986237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,33 +1282,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127124770</v>
+        <v>127123720</v>
       </c>
       <c r="B8" t="n">
-        <v>98363</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1327,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595711</v>
+        <v>595830</v>
       </c>
       <c r="R8" t="n">
-        <v>6986237</v>
+        <v>6986436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1358,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127124585</v>
+        <v>127125706</v>
       </c>
       <c r="B11" t="n">
-        <v>80117</v>
+        <v>80083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595752</v>
+        <v>595873</v>
       </c>
       <c r="R11" t="n">
-        <v>6986290</v>
+        <v>6986327</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127125706</v>
+        <v>127124585</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595873</v>
+        <v>595752</v>
       </c>
       <c r="R12" t="n">
-        <v>6986327</v>
+        <v>6986290</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127123933</v>
+        <v>127125760</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>80077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595828</v>
+        <v>595888</v>
       </c>
       <c r="R13" t="n">
-        <v>6986375</v>
+        <v>6986327</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,32 +1874,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127124329</v>
+        <v>127123933</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595748</v>
+        <v>595828</v>
       </c>
       <c r="R14" t="n">
-        <v>6986317</v>
+        <v>6986375</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127125760</v>
+        <v>127124329</v>
       </c>
       <c r="B15" t="n">
-        <v>80077</v>
+        <v>91326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595888</v>
+        <v>595748</v>
       </c>
       <c r="R15" t="n">
-        <v>6986327</v>
+        <v>6986317</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124805</v>
+        <v>127124387</v>
       </c>
       <c r="B18" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595706</v>
+        <v>595748</v>
       </c>
       <c r="R18" t="n">
-        <v>6986223</v>
+        <v>6986317</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2374,7 +2379,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124387</v>
+        <v>127123757</v>
       </c>
       <c r="B19" t="n">
         <v>57657</v>
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595748</v>
+        <v>595824</v>
       </c>
       <c r="R19" t="n">
-        <v>6986317</v>
+        <v>6986427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127123757</v>
+        <v>127124805</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,16 +2497,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595824</v>
+        <v>595706</v>
       </c>
       <c r="R20" t="n">
-        <v>6986427</v>
+        <v>6986223</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,11 +2562,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -1185,33 +1185,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127124770</v>
+        <v>127123720</v>
       </c>
       <c r="B7" t="n">
-        <v>98363</v>
+        <v>57657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1220,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595711</v>
+        <v>595830</v>
       </c>
       <c r="R7" t="n">
-        <v>6986237</v>
+        <v>6986436</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,38 +1292,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127123720</v>
+        <v>127124770</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>98363</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1322,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595830</v>
+        <v>595711</v>
       </c>
       <c r="R8" t="n">
-        <v>6986436</v>
+        <v>6986237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125760</v>
+        <v>127123933</v>
       </c>
       <c r="B13" t="n">
-        <v>80077</v>
+        <v>80146</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595888</v>
+        <v>595828</v>
       </c>
       <c r="R13" t="n">
-        <v>6986327</v>
+        <v>6986375</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,32 +1874,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127123933</v>
+        <v>127124329</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>91326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595828</v>
+        <v>595748</v>
       </c>
       <c r="R14" t="n">
-        <v>6986375</v>
+        <v>6986317</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127124329</v>
+        <v>127125760</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>80077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595748</v>
+        <v>595888</v>
       </c>
       <c r="R15" t="n">
-        <v>6986317</v>
+        <v>6986327</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127123933</v>
+        <v>127125760</v>
       </c>
       <c r="B13" t="n">
-        <v>80146</v>
+        <v>80077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595828</v>
+        <v>595888</v>
       </c>
       <c r="R13" t="n">
-        <v>6986375</v>
+        <v>6986327</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,32 +1874,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127124329</v>
+        <v>127123933</v>
       </c>
       <c r="B14" t="n">
-        <v>91326</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595748</v>
+        <v>595828</v>
       </c>
       <c r="R14" t="n">
-        <v>6986317</v>
+        <v>6986375</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127125760</v>
+        <v>127124329</v>
       </c>
       <c r="B15" t="n">
-        <v>80077</v>
+        <v>91326</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595888</v>
+        <v>595748</v>
       </c>
       <c r="R15" t="n">
-        <v>6986327</v>
+        <v>6986317</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,50 +2272,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124387</v>
+        <v>127124623</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>97324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595748</v>
+        <v>595755</v>
       </c>
       <c r="R18" t="n">
-        <v>6986317</v>
+        <v>6986253</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2343,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2369,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127123757</v>
+        <v>127124387</v>
       </c>
       <c r="B19" t="n">
         <v>57657</v>
@@ -2419,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595824</v>
+        <v>595748</v>
       </c>
       <c r="R19" t="n">
-        <v>6986427</v>
+        <v>6986317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124805</v>
+        <v>127123757</v>
       </c>
       <c r="B20" t="n">
-        <v>57654</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,16 +2487,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2526,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595706</v>
+        <v>595824</v>
       </c>
       <c r="R20" t="n">
-        <v>6986223</v>
+        <v>6986427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,6 +2552,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,45 +2583,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124623</v>
+        <v>127124805</v>
       </c>
       <c r="B21" t="n">
-        <v>97324</v>
+        <v>57654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595755</v>
+        <v>595706</v>
       </c>
       <c r="R21" t="n">
-        <v>6986253</v>
+        <v>6986223</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127123992</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127123617</v>
       </c>
       <c r="B3" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127123865</v>
       </c>
       <c r="B4" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127125627</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127123849</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,38 +1185,33 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127123720</v>
+        <v>127124770</v>
       </c>
       <c r="B7" t="n">
-        <v>57657</v>
+        <v>98367</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595830</v>
+        <v>595711</v>
       </c>
       <c r="R7" t="n">
-        <v>6986436</v>
+        <v>6986237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,33 +1282,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127124770</v>
+        <v>127123720</v>
       </c>
       <c r="B8" t="n">
-        <v>98363</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1327,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595711</v>
+        <v>595830</v>
       </c>
       <c r="R8" t="n">
-        <v>6986237</v>
+        <v>6986436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1358,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,7 +1392,7 @@
         <v>127124162</v>
       </c>
       <c r="B9" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127123771</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>127125706</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>80087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127124585</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125760</v>
+        <v>127123933</v>
       </c>
       <c r="B13" t="n">
-        <v>80077</v>
+        <v>80150</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595888</v>
+        <v>595828</v>
       </c>
       <c r="R13" t="n">
-        <v>6986327</v>
+        <v>6986375</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,32 +1874,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127123933</v>
+        <v>127124329</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>91330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595828</v>
+        <v>595748</v>
       </c>
       <c r="R14" t="n">
-        <v>6986375</v>
+        <v>6986317</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127124329</v>
+        <v>127125760</v>
       </c>
       <c r="B15" t="n">
-        <v>91326</v>
+        <v>80081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595748</v>
+        <v>595888</v>
       </c>
       <c r="R15" t="n">
-        <v>6986317</v>
+        <v>6986327</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
         <v>127125279</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2168,7 +2168,7 @@
         <v>127125418</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2272,45 +2272,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124623</v>
+        <v>127124387</v>
       </c>
       <c r="B18" t="n">
-        <v>97324</v>
+        <v>57661</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595755</v>
+        <v>595748</v>
       </c>
       <c r="R18" t="n">
-        <v>6986253</v>
+        <v>6986317</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2369,10 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124387</v>
+        <v>127123757</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2409,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595748</v>
+        <v>595824</v>
       </c>
       <c r="R19" t="n">
-        <v>6986317</v>
+        <v>6986427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127123757</v>
+        <v>127124805</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57658</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2487,16 +2497,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2516,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595824</v>
+        <v>595706</v>
       </c>
       <c r="R20" t="n">
-        <v>6986427</v>
+        <v>6986223</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,11 +2562,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124805</v>
+        <v>127124623</v>
       </c>
       <c r="B21" t="n">
-        <v>57654</v>
+        <v>97328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595706</v>
+        <v>595755</v>
       </c>
       <c r="R21" t="n">
-        <v>6986223</v>
+        <v>6986253</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
         <v>127123740</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127427818</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>127427830</v>
       </c>
       <c r="B24" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>127427437</v>
       </c>
       <c r="B25" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>127428796</v>
       </c>
       <c r="B26" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127427844</v>
       </c>
       <c r="B27" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127125706</v>
+        <v>127124585</v>
       </c>
       <c r="B11" t="n">
-        <v>80087</v>
+        <v>80121</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595873</v>
+        <v>595752</v>
       </c>
       <c r="R11" t="n">
-        <v>6986327</v>
+        <v>6986290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127124585</v>
+        <v>127125706</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>80087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595752</v>
+        <v>595873</v>
       </c>
       <c r="R12" t="n">
-        <v>6986290</v>
+        <v>6986327</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127123933</v>
+        <v>127124329</v>
       </c>
       <c r="B13" t="n">
-        <v>80150</v>
+        <v>91330</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595828</v>
+        <v>595748</v>
       </c>
       <c r="R13" t="n">
-        <v>6986375</v>
+        <v>6986317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,32 +1874,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127124329</v>
+        <v>127123933</v>
       </c>
       <c r="B14" t="n">
-        <v>91330</v>
+        <v>80150</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595748</v>
+        <v>595828</v>
       </c>
       <c r="R14" t="n">
-        <v>6986317</v>
+        <v>6986375</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2272,50 +2272,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124387</v>
+        <v>127124623</v>
       </c>
       <c r="B18" t="n">
-        <v>57661</v>
+        <v>97328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595748</v>
+        <v>595755</v>
       </c>
       <c r="R18" t="n">
-        <v>6986317</v>
+        <v>6986253</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2343,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,10 +2369,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127123757</v>
+        <v>127124805</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2390,16 +2380,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2419,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595824</v>
+        <v>595706</v>
       </c>
       <c r="R19" t="n">
-        <v>6986427</v>
+        <v>6986223</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2455,11 +2445,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2486,10 +2471,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124805</v>
+        <v>127124387</v>
       </c>
       <c r="B20" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,16 +2482,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2526,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595706</v>
+        <v>595748</v>
       </c>
       <c r="R20" t="n">
-        <v>6986223</v>
+        <v>6986317</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,6 +2547,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,45 +2578,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124623</v>
+        <v>127123757</v>
       </c>
       <c r="B21" t="n">
-        <v>97328</v>
+        <v>57661</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595755</v>
+        <v>595824</v>
       </c>
       <c r="R21" t="n">
-        <v>6986253</v>
+        <v>6986427</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127125627</v>
+        <v>127123849</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595873</v>
+        <v>595811</v>
       </c>
       <c r="R5" t="n">
-        <v>6986327</v>
+        <v>6986388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127123849</v>
+        <v>127125627</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595811</v>
+        <v>595873</v>
       </c>
       <c r="R6" t="n">
-        <v>6986388</v>
+        <v>6986327</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,33 +1185,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127124770</v>
+        <v>127123720</v>
       </c>
       <c r="B7" t="n">
-        <v>98367</v>
+        <v>57661</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1220,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595711</v>
+        <v>595830</v>
       </c>
       <c r="R7" t="n">
-        <v>6986237</v>
+        <v>6986436</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,38 +1292,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127123720</v>
+        <v>127124770</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>98368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1322,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595830</v>
+        <v>595711</v>
       </c>
       <c r="R8" t="n">
-        <v>6986436</v>
+        <v>6986237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2272,45 +2272,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124623</v>
+        <v>127124805</v>
       </c>
       <c r="B18" t="n">
-        <v>97328</v>
+        <v>57658</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595755</v>
+        <v>595706</v>
       </c>
       <c r="R18" t="n">
-        <v>6986253</v>
+        <v>6986223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124805</v>
+        <v>127124387</v>
       </c>
       <c r="B19" t="n">
-        <v>57658</v>
+        <v>57661</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2380,16 +2385,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2409,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595706</v>
+        <v>595748</v>
       </c>
       <c r="R19" t="n">
-        <v>6986223</v>
+        <v>6986317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2471,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124387</v>
+        <v>127123757</v>
       </c>
       <c r="B20" t="n">
         <v>57661</v>
@@ -2511,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595748</v>
+        <v>595824</v>
       </c>
       <c r="R20" t="n">
-        <v>6986317</v>
+        <v>6986427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127123757</v>
+        <v>127124623</v>
       </c>
       <c r="B21" t="n">
-        <v>57661</v>
+        <v>97328</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595824</v>
+        <v>595755</v>
       </c>
       <c r="R21" t="n">
-        <v>6986427</v>
+        <v>6986253</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2795,7 @@
         <v>127427818</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127123849</v>
+        <v>127125627</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595811</v>
+        <v>595873</v>
       </c>
       <c r="R5" t="n">
-        <v>6986388</v>
+        <v>6986327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127125627</v>
+        <v>127123849</v>
       </c>
       <c r="B6" t="n">
-        <v>80150</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595873</v>
+        <v>595811</v>
       </c>
       <c r="R6" t="n">
-        <v>6986327</v>
+        <v>6986388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127124585</v>
+        <v>127125706</v>
       </c>
       <c r="B11" t="n">
-        <v>80121</v>
+        <v>80087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595752</v>
+        <v>595873</v>
       </c>
       <c r="R11" t="n">
-        <v>6986290</v>
+        <v>6986327</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127125706</v>
+        <v>127124585</v>
       </c>
       <c r="B12" t="n">
-        <v>80087</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595873</v>
+        <v>595752</v>
       </c>
       <c r="R12" t="n">
-        <v>6986327</v>
+        <v>6986290</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127123992</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127123617</v>
       </c>
       <c r="B3" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>127123865</v>
       </c>
       <c r="B4" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>127125627</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127123849</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127123720</v>
       </c>
       <c r="B7" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>127124770</v>
       </c>
       <c r="B8" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127124162</v>
       </c>
       <c r="B9" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127123771</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>127125706</v>
       </c>
       <c r="B11" t="n">
-        <v>80087</v>
+        <v>80089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>127124585</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>127124329</v>
       </c>
       <c r="B13" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>127123933</v>
       </c>
       <c r="B14" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>127125760</v>
       </c>
       <c r="B15" t="n">
-        <v>80081</v>
+        <v>80083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127125279</v>
+        <v>127125418</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,34 +2079,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595812</v>
+        <v>595850</v>
       </c>
       <c r="R16" t="n">
-        <v>6986327</v>
+        <v>6986354</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,6 +2144,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2165,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125418</v>
+        <v>127125279</v>
       </c>
       <c r="B17" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2176,39 +2186,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595850</v>
+        <v>595812</v>
       </c>
       <c r="R17" t="n">
-        <v>6986354</v>
+        <v>6986327</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2241,11 +2246,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2275,7 +2275,7 @@
         <v>127124805</v>
       </c>
       <c r="B18" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124387</v>
+        <v>127123757</v>
       </c>
       <c r="B19" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595748</v>
+        <v>595824</v>
       </c>
       <c r="R19" t="n">
-        <v>6986317</v>
+        <v>6986427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127123757</v>
+        <v>127124387</v>
       </c>
       <c r="B20" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595824</v>
+        <v>595748</v>
       </c>
       <c r="R20" t="n">
-        <v>6986427</v>
+        <v>6986317</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,7 +2591,7 @@
         <v>127124623</v>
       </c>
       <c r="B21" t="n">
-        <v>97328</v>
+        <v>97330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2688,7 +2688,7 @@
         <v>127123740</v>
       </c>
       <c r="B22" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127427818</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>127427830</v>
       </c>
       <c r="B24" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>127427437</v>
       </c>
       <c r="B25" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>127428796</v>
       </c>
       <c r="B26" t="n">
-        <v>91295</v>
+        <v>91297</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127427844</v>
       </c>
       <c r="B27" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127125627</v>
+        <v>127123849</v>
       </c>
       <c r="B5" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595873</v>
+        <v>595811</v>
       </c>
       <c r="R5" t="n">
-        <v>6986327</v>
+        <v>6986388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127123849</v>
+        <v>127125627</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>80152</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595811</v>
+        <v>595873</v>
       </c>
       <c r="R6" t="n">
-        <v>6986388</v>
+        <v>6986327</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,38 +1185,33 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127123720</v>
+        <v>127124770</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>98370</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595830</v>
+        <v>595711</v>
       </c>
       <c r="R7" t="n">
-        <v>6986436</v>
+        <v>6986237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,33 +1282,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127124770</v>
+        <v>127123720</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1327,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595711</v>
+        <v>595830</v>
       </c>
       <c r="R8" t="n">
-        <v>6986237</v>
+        <v>6986436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1358,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -2272,10 +2272,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124805</v>
+        <v>127124387</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2283,16 +2283,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595706</v>
+        <v>595748</v>
       </c>
       <c r="R18" t="n">
-        <v>6986223</v>
+        <v>6986317</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,6 +2348,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2481,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124387</v>
+        <v>127124805</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>57660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,16 +2497,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2521,10 +2526,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595748</v>
+        <v>595706</v>
       </c>
       <c r="R20" t="n">
-        <v>6986317</v>
+        <v>6986223</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2557,11 +2562,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127123617</v>
+        <v>127123865</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,27 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595826</v>
+        <v>595811</v>
       </c>
       <c r="R3" t="n">
-        <v>6986441</v>
+        <v>6986388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127123865</v>
+        <v>127123617</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,27 +895,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595811</v>
+        <v>595826</v>
       </c>
       <c r="R4" t="n">
-        <v>6986388</v>
+        <v>6986441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127123849</v>
+        <v>127125627</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>80152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595811</v>
+        <v>595873</v>
       </c>
       <c r="R5" t="n">
-        <v>6986388</v>
+        <v>6986327</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,32 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127125627</v>
+        <v>127123849</v>
       </c>
       <c r="B6" t="n">
-        <v>80152</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595873</v>
+        <v>595811</v>
       </c>
       <c r="R6" t="n">
-        <v>6986327</v>
+        <v>6986388</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127125706</v>
+        <v>127124585</v>
       </c>
       <c r="B11" t="n">
-        <v>80089</v>
+        <v>80123</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595873</v>
+        <v>595752</v>
       </c>
       <c r="R11" t="n">
-        <v>6986327</v>
+        <v>6986290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127124585</v>
+        <v>127125706</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>80089</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595752</v>
+        <v>595873</v>
       </c>
       <c r="R12" t="n">
-        <v>6986290</v>
+        <v>6986327</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2272,50 +2272,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124387</v>
+        <v>127124623</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>97330</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595748</v>
+        <v>595755</v>
       </c>
       <c r="R18" t="n">
-        <v>6986317</v>
+        <v>6986253</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2348,11 +2343,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2379,7 +2369,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127123757</v>
+        <v>127124387</v>
       </c>
       <c r="B19" t="n">
         <v>57663</v>
@@ -2419,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595824</v>
+        <v>595748</v>
       </c>
       <c r="R19" t="n">
-        <v>6986427</v>
+        <v>6986317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,10 +2476,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124805</v>
+        <v>127123757</v>
       </c>
       <c r="B20" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,16 +2487,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2526,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595706</v>
+        <v>595824</v>
       </c>
       <c r="R20" t="n">
-        <v>6986223</v>
+        <v>6986427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2562,6 +2552,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,45 +2583,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124623</v>
+        <v>127124805</v>
       </c>
       <c r="B21" t="n">
-        <v>97330</v>
+        <v>57660</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595755</v>
+        <v>595706</v>
       </c>
       <c r="R21" t="n">
-        <v>6986253</v>
+        <v>6986223</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127123865</v>
+        <v>127123617</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,27 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595811</v>
+        <v>595826</v>
       </c>
       <c r="R3" t="n">
-        <v>6986388</v>
+        <v>6986441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127123617</v>
+        <v>127123865</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,27 +900,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595826</v>
+        <v>595811</v>
       </c>
       <c r="R4" t="n">
-        <v>6986441</v>
+        <v>6986388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1188,7 +1188,7 @@
         <v>127124770</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127124162</v>
       </c>
       <c r="B9" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127124329</v>
+        <v>127125760</v>
       </c>
       <c r="B13" t="n">
-        <v>91332</v>
+        <v>80083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595748</v>
+        <v>595888</v>
       </c>
       <c r="R13" t="n">
-        <v>6986317</v>
+        <v>6986327</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,32 +1874,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127123933</v>
+        <v>127124329</v>
       </c>
       <c r="B14" t="n">
-        <v>80152</v>
+        <v>91338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595828</v>
+        <v>595748</v>
       </c>
       <c r="R14" t="n">
-        <v>6986375</v>
+        <v>6986317</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127125760</v>
+        <v>127123933</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80152</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595888</v>
+        <v>595828</v>
       </c>
       <c r="R15" t="n">
-        <v>6986327</v>
+        <v>6986375</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127125418</v>
+        <v>127125279</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,39 +2079,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595850</v>
+        <v>595812</v>
       </c>
       <c r="R16" t="n">
-        <v>6986354</v>
+        <v>6986327</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,11 +2139,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2175,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125279</v>
+        <v>127125418</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,34 +2176,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595812</v>
+        <v>595850</v>
       </c>
       <c r="R17" t="n">
-        <v>6986327</v>
+        <v>6986354</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2246,6 +2241,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2272,45 +2272,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127124623</v>
+        <v>127124805</v>
       </c>
       <c r="B18" t="n">
-        <v>97330</v>
+        <v>57660</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>595755</v>
+        <v>595706</v>
       </c>
       <c r="R18" t="n">
-        <v>6986253</v>
+        <v>6986223</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2369,50 +2374,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124387</v>
+        <v>127124623</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>97336</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>221946</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595748</v>
+        <v>595755</v>
       </c>
       <c r="R19" t="n">
-        <v>6986317</v>
+        <v>6986253</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,11 +2445,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2476,7 +2471,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127123757</v>
+        <v>127124387</v>
       </c>
       <c r="B20" t="n">
         <v>57663</v>
@@ -2516,10 +2511,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595824</v>
+        <v>595748</v>
       </c>
       <c r="R20" t="n">
-        <v>6986427</v>
+        <v>6986317</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2583,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124805</v>
+        <v>127123757</v>
       </c>
       <c r="B21" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,16 +2589,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2623,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595706</v>
+        <v>595824</v>
       </c>
       <c r="R21" t="n">
-        <v>6986223</v>
+        <v>6986427</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,6 +2654,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,7 +2795,7 @@
         <v>127427818</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>127427437</v>
       </c>
       <c r="B25" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>127428796</v>
       </c>
       <c r="B26" t="n">
-        <v>91297</v>
+        <v>91303</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127427844</v>
       </c>
       <c r="B27" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127123992</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127123617</v>
+        <v>127123865</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57826</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,27 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595826</v>
+        <v>595811</v>
       </c>
       <c r="R3" t="n">
-        <v>6986441</v>
+        <v>6986388</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127123865</v>
+        <v>127123617</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,27 +895,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595811</v>
+        <v>595826</v>
       </c>
       <c r="R4" t="n">
-        <v>6986388</v>
+        <v>6986441</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +994,7 @@
         <v>127125627</v>
       </c>
       <c r="B5" t="n">
-        <v>80152</v>
+        <v>80155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127123849</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1185,33 +1185,38 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127124770</v>
+        <v>127123720</v>
       </c>
       <c r="B7" t="n">
-        <v>98376</v>
+        <v>57666</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1220,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595711</v>
+        <v>595830</v>
       </c>
       <c r="R7" t="n">
-        <v>6986237</v>
+        <v>6986436</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1256,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1282,38 +1292,33 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127123720</v>
+        <v>127124770</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>98379</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1322,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595830</v>
+        <v>595711</v>
       </c>
       <c r="R8" t="n">
-        <v>6986436</v>
+        <v>6986237</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1392,7 +1392,7 @@
         <v>127124162</v>
       </c>
       <c r="B9" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127123771</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127124585</v>
+        <v>127125706</v>
       </c>
       <c r="B11" t="n">
-        <v>80123</v>
+        <v>80092</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595752</v>
+        <v>595873</v>
       </c>
       <c r="R11" t="n">
-        <v>6986290</v>
+        <v>6986327</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127125706</v>
+        <v>127124585</v>
       </c>
       <c r="B12" t="n">
-        <v>80089</v>
+        <v>80126</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595873</v>
+        <v>595752</v>
       </c>
       <c r="R12" t="n">
-        <v>6986327</v>
+        <v>6986290</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125760</v>
+        <v>127124329</v>
       </c>
       <c r="B13" t="n">
-        <v>80083</v>
+        <v>91341</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595888</v>
+        <v>595748</v>
       </c>
       <c r="R13" t="n">
-        <v>6986327</v>
+        <v>6986317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,32 +1874,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127124329</v>
+        <v>127123933</v>
       </c>
       <c r="B14" t="n">
-        <v>91338</v>
+        <v>80155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595748</v>
+        <v>595828</v>
       </c>
       <c r="R14" t="n">
-        <v>6986317</v>
+        <v>6986375</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127123933</v>
+        <v>127125760</v>
       </c>
       <c r="B15" t="n">
-        <v>80152</v>
+        <v>80086</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1982,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595828</v>
+        <v>595888</v>
       </c>
       <c r="R15" t="n">
-        <v>6986375</v>
+        <v>6986327</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127125279</v>
+        <v>127125418</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>57666</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,34 +2079,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595812</v>
+        <v>595850</v>
       </c>
       <c r="R16" t="n">
-        <v>6986327</v>
+        <v>6986354</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,6 +2144,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2165,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125418</v>
+        <v>127125279</v>
       </c>
       <c r="B17" t="n">
-        <v>57663</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2176,39 +2186,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595850</v>
+        <v>595812</v>
       </c>
       <c r="R17" t="n">
-        <v>6986354</v>
+        <v>6986327</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2241,11 +2246,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2275,7 +2275,7 @@
         <v>127124805</v>
       </c>
       <c r="B18" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,45 +2374,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127124623</v>
+        <v>127123757</v>
       </c>
       <c r="B19" t="n">
-        <v>97336</v>
+        <v>57666</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595755</v>
+        <v>595824</v>
       </c>
       <c r="R19" t="n">
-        <v>6986253</v>
+        <v>6986427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2445,6 +2450,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2471,50 +2481,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124387</v>
+        <v>127124623</v>
       </c>
       <c r="B20" t="n">
-        <v>57663</v>
+        <v>97339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>221946</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595748</v>
+        <v>595755</v>
       </c>
       <c r="R20" t="n">
-        <v>6986317</v>
+        <v>6986253</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,11 +2552,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127123757</v>
+        <v>127124387</v>
       </c>
       <c r="B21" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595824</v>
+        <v>595748</v>
       </c>
       <c r="R21" t="n">
-        <v>6986427</v>
+        <v>6986317</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,7 +2688,7 @@
         <v>127123740</v>
       </c>
       <c r="B22" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127427818</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>127427830</v>
       </c>
       <c r="B24" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>127427437</v>
       </c>
       <c r="B25" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>127428796</v>
       </c>
       <c r="B26" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127427844</v>
       </c>
       <c r="B27" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127123992</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127123865</v>
+        <v>127123617</v>
       </c>
       <c r="B3" t="n">
-        <v>57826</v>
+        <v>57672</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,27 +793,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595811</v>
+        <v>595826</v>
       </c>
       <c r="R3" t="n">
-        <v>6986388</v>
+        <v>6986441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127123617</v>
+        <v>127123865</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,27 +900,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>595826</v>
+        <v>595811</v>
       </c>
       <c r="R4" t="n">
-        <v>6986441</v>
+        <v>6986388</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +994,7 @@
         <v>127125627</v>
       </c>
       <c r="B5" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>127123849</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>127123720</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>127124770</v>
       </c>
       <c r="B8" t="n">
-        <v>98379</v>
+        <v>98387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>127124162</v>
       </c>
       <c r="B9" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>127123771</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,32 +1583,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127125706</v>
+        <v>127124585</v>
       </c>
       <c r="B11" t="n">
-        <v>80092</v>
+        <v>80132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229748</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1618,10 +1618,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>595873</v>
+        <v>595752</v>
       </c>
       <c r="R11" t="n">
-        <v>6986327</v>
+        <v>6986290</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1680,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127124585</v>
+        <v>127125706</v>
       </c>
       <c r="B12" t="n">
-        <v>80126</v>
+        <v>80098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>229748</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>595752</v>
+        <v>595873</v>
       </c>
       <c r="R12" t="n">
-        <v>6986290</v>
+        <v>6986327</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127124329</v>
+        <v>127125760</v>
       </c>
       <c r="B13" t="n">
-        <v>91341</v>
+        <v>80092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595748</v>
+        <v>595888</v>
       </c>
       <c r="R13" t="n">
-        <v>6986317</v>
+        <v>6986327</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1877,7 +1877,7 @@
         <v>127123933</v>
       </c>
       <c r="B14" t="n">
-        <v>80155</v>
+        <v>80161</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127125760</v>
+        <v>127124329</v>
       </c>
       <c r="B15" t="n">
-        <v>80086</v>
+        <v>91349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595888</v>
+        <v>595748</v>
       </c>
       <c r="R15" t="n">
-        <v>6986327</v>
+        <v>6986317</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127125418</v>
+        <v>127125279</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,39 +2079,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595850</v>
+        <v>595812</v>
       </c>
       <c r="R16" t="n">
-        <v>6986354</v>
+        <v>6986327</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2144,11 +2139,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2175,10 +2165,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125279</v>
+        <v>127125418</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2186,34 +2176,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595812</v>
+        <v>595850</v>
       </c>
       <c r="R17" t="n">
-        <v>6986327</v>
+        <v>6986354</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2246,6 +2241,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2275,7 +2275,7 @@
         <v>127124805</v>
       </c>
       <c r="B18" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2374,10 +2374,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127123757</v>
+        <v>127124387</v>
       </c>
       <c r="B19" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>595824</v>
+        <v>595748</v>
       </c>
       <c r="R19" t="n">
-        <v>6986427</v>
+        <v>6986317</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,45 +2481,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124623</v>
+        <v>127123757</v>
       </c>
       <c r="B20" t="n">
-        <v>97339</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221946</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595755</v>
+        <v>595824</v>
       </c>
       <c r="R20" t="n">
-        <v>6986253</v>
+        <v>6986427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2552,6 +2557,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,50 +2588,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124387</v>
+        <v>127124623</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>97347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221946</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>595748</v>
+        <v>595755</v>
       </c>
       <c r="R21" t="n">
-        <v>6986317</v>
+        <v>6986253</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2654,11 +2659,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2688,7 +2688,7 @@
         <v>127123740</v>
       </c>
       <c r="B22" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         <v>127427818</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>127427830</v>
       </c>
       <c r="B24" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>127427437</v>
       </c>
       <c r="B25" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>127428796</v>
       </c>
       <c r="B26" t="n">
-        <v>91306</v>
+        <v>91314</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127427844</v>
       </c>
       <c r="B27" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -1185,38 +1185,33 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127123720</v>
+        <v>127124770</v>
       </c>
       <c r="B7" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>223597</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1225,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595830</v>
+        <v>595711</v>
       </c>
       <c r="R7" t="n">
-        <v>6986436</v>
+        <v>6986237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,11 +1256,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,33 +1282,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127124770</v>
+        <v>127123720</v>
       </c>
       <c r="B8" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>223597</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1327,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595711</v>
+        <v>595830</v>
       </c>
       <c r="R8" t="n">
-        <v>6986237</v>
+        <v>6986436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1358,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1777,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125760</v>
+        <v>127124329</v>
       </c>
       <c r="B13" t="n">
-        <v>80092</v>
+        <v>91349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595888</v>
+        <v>595748</v>
       </c>
       <c r="R13" t="n">
-        <v>6986327</v>
+        <v>6986317</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127123933</v>
+        <v>127125760</v>
       </c>
       <c r="B14" t="n">
-        <v>80161</v>
+        <v>80092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1885,21 +1885,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595828</v>
+        <v>595888</v>
       </c>
       <c r="R14" t="n">
-        <v>6986375</v>
+        <v>6986327</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,32 +1971,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127124329</v>
+        <v>127123933</v>
       </c>
       <c r="B15" t="n">
-        <v>91349</v>
+        <v>80161</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595748</v>
+        <v>595828</v>
       </c>
       <c r="R15" t="n">
-        <v>6986317</v>
+        <v>6986375</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,10 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127125279</v>
+        <v>127125418</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2079,34 +2079,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595812</v>
+        <v>595850</v>
       </c>
       <c r="R16" t="n">
-        <v>6986327</v>
+        <v>6986354</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2139,6 +2144,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2165,10 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125418</v>
+        <v>127125279</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2176,39 +2186,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Högåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>595850</v>
+        <v>595812</v>
       </c>
       <c r="R17" t="n">
-        <v>6986354</v>
+        <v>6986327</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2241,11 +2246,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2795,7 +2795,7 @@
         <v>127427818</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>127427437</v>
       </c>
       <c r="B25" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>127428796</v>
       </c>
       <c r="B26" t="n">
-        <v>91314</v>
+        <v>91315</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127427844</v>
       </c>
       <c r="B27" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -2795,7 +2795,7 @@
         <v>127427818</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>127427437</v>
       </c>
       <c r="B25" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>127428796</v>
       </c>
       <c r="B26" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127427844</v>
       </c>
       <c r="B27" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -2795,7 +2795,7 @@
         <v>127427818</v>
       </c>
       <c r="B23" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>127427437</v>
       </c>
       <c r="B25" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>127428796</v>
       </c>
       <c r="B26" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>127427844</v>
       </c>
       <c r="B27" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3279,6 +3279,344 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129297443</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Galantmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>595822</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6986427</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>FÃ¤rska ringhack pÃ¥ tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129297445</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Galantmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>595771</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6986242</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129297444</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Galantmyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>595858</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6986388</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129297444</v>
       </c>
       <c r="B30" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3284,7 +3284,7 @@
         <v>129297443</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129297444</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129297444</v>
       </c>
       <c r="B30" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129297444</v>
       </c>
       <c r="B30" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3616,6 +3616,641 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129431276</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>595852</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6986355</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129431277</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>595822</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6986430</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gran.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129431273</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>595784</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6986398</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129431275</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>595826</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6986365</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129431272</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>595744</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6986316</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129431274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57727</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ödingen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>595799</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6986416</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129297444</v>
       </c>
       <c r="B30" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129297444</v>
       </c>
       <c r="B30" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129297444</v>
       </c>
       <c r="B30" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129297444</v>
       </c>
       <c r="B30" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 22985-2025 artfynd.xlsx
+++ b/artfynd/A 22985-2025 artfynd.xlsx
@@ -3284,7 +3284,7 @@
         <v>129297443</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>129297445</v>
       </c>
       <c r="B29" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>129297444</v>
       </c>
       <c r="B30" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>129431276</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>129431277</v>
       </c>
       <c r="B32" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3837,7 +3837,7 @@
         <v>129431273</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>129431275</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>129431272</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4152,7 +4152,7 @@
         <v>129431274</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
